--- a/05_내역서/내역서작업/01_화성 청원지구 조경_표준단가산출.xlsx
+++ b/05_내역서/내역서작업/01_화성 청원지구 조경_표준단가산출.xlsx
@@ -17,9 +17,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'합계요약'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'통합내역'!$A$1:$T$81</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'매칭내역'!$A$1:$S$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'검토필요'!$A$1:$S$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'미매칭'!$A$1:$H$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'매칭내역'!$A$1:$S$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'검토필요'!$A$1:$S$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'미매칭'!$A$1:$H$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -505,7 +505,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>조달청 표준시장단가 (표준시장단가2026 6,347 + 시장시공가격 575 + 표준일위대가2026 10,765 + 물가정보2026 15 + 조달청시설자재2026 6,110 + 조경일위대가2024 1,039건)</t>
+          <t>조달청 표준시장단가 (표준시장단가2026 + forestinfo 조경수(주 31건) + 조경일위2024 식재노무)</t>
         </is>
       </c>
     </row>
@@ -650,8 +650,8 @@
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="4" customWidth="1" min="2" max="2"/>
     <col width="4" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
@@ -706,25 +706,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>80</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.3625</v>
+        <v>0.75</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>12109080</v>
+        <v>167873580</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>106764222</v>
+        <v>263715320</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>2136313</v>
+        <v>5849219</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>121009615</v>
+        <v>437438119</v>
       </c>
     </row>
     <row r="3">
@@ -744,25 +744,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>80</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.3625</v>
+        <v>0.75</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>12109080</v>
+        <v>167873580</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>106764222</v>
+        <v>263715320</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>2136313</v>
+        <v>5849219</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>121009615</v>
+        <v>437438119</v>
       </c>
     </row>
     <row r="5">
@@ -772,13 +772,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>80</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.6375</v>
+        <v>0.25</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0</v>
@@ -819,13 +819,13 @@
     <col width="32" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="31" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="26" customWidth="1" min="20" max="20"/>
   </cols>
@@ -1009,470 +1009,722 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="n">
+      <c r="A3" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>나). 스트로브잣</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>H3.5xW1.8</t>
         </is>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="n">
-        <v>0.392</v>
-      </c>
-      <c r="I3" s="8" t="inlineStr"/>
-      <c r="J3" s="8" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="8" t="inlineStr"/>
-      <c r="M3" s="8" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
-      <c r="O3" s="8" t="inlineStr"/>
-      <c r="P3" s="8" t="inlineStr"/>
-      <c r="Q3" s="8" t="inlineStr"/>
-      <c r="R3" s="8" t="inlineStr"/>
-      <c r="S3" s="8" t="inlineStr"/>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xW1.8, 스트로브잣</t>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|스트로브잣나무|H3.5XW1.8</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>스트로브잣나무</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xW1.8</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>64009</v>
+      </c>
+      <c r="N3" s="5" t="n">
+        <v>6551</v>
+      </c>
+      <c r="O3" s="5" t="n">
+        <v>220560</v>
+      </c>
+      <c r="P3" s="5" t="n">
+        <v>8250000</v>
+      </c>
+      <c r="Q3" s="5" t="n">
+        <v>3520495</v>
+      </c>
+      <c r="R3" s="5" t="n">
+        <v>360305</v>
+      </c>
+      <c r="S3" s="5" t="n">
+        <v>12130800</v>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.00</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>다). 느티나무</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>H4.0xR15</t>
         </is>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="I4" s="8" t="inlineStr"/>
-      <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="8" t="inlineStr"/>
-      <c r="M4" s="8" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
-      <c r="O4" s="8" t="inlineStr"/>
-      <c r="P4" s="8" t="inlineStr"/>
-      <c r="Q4" s="8" t="inlineStr"/>
-      <c r="R4" s="8" t="inlineStr"/>
-      <c r="S4" s="8" t="inlineStr"/>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>H4.0xR15, 느티나무</t>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|느티나무|R15</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>느티나무</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>H4.0xR15</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>270000</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>106589</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>10907</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>387496</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>1890000</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>746123</v>
+      </c>
+      <c r="R4" s="5" t="n">
+        <v>76349</v>
+      </c>
+      <c r="S4" s="5" t="n">
+        <v>2712472</v>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.17</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>라). 배롱나무</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>H3.0xR10</t>
         </is>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="8" t="inlineStr"/>
-      <c r="M5" s="8" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
-      <c r="O5" s="8" t="inlineStr"/>
-      <c r="P5" s="8" t="inlineStr"/>
-      <c r="Q5" s="8" t="inlineStr"/>
-      <c r="R5" s="8" t="inlineStr"/>
-      <c r="S5" s="8" t="inlineStr"/>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>H3.0xR10, 배롱나무</t>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|배롱나무|H3.0XR10</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>배롱나무</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>H3.0xR10</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>170000</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>75029</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>7697</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>252726</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>510000</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>225087</v>
+      </c>
+      <c r="R5" s="5" t="n">
+        <v>23091</v>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>758178</v>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.00</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>마). 왕벚나무</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>H3.5xB8</t>
         </is>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="I6" s="8" t="inlineStr"/>
-      <c r="J6" s="8" t="inlineStr"/>
-      <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="8" t="inlineStr"/>
-      <c r="M6" s="8" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
-      <c r="O6" s="8" t="inlineStr"/>
-      <c r="P6" s="8" t="inlineStr"/>
-      <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="8" t="inlineStr"/>
-      <c r="S6" s="8" t="inlineStr"/>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xB8, 왕벚나무</t>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|왕벚나무|B8</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>왕벚나무</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xB8</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>130000</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>64009</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>6551</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>200560</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>1040000</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>512072</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>52408</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>1604480</v>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.17</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>바). 청단풍</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>H3.0xR8</t>
         </is>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="I7" s="8" t="inlineStr"/>
-      <c r="J7" s="8" t="inlineStr"/>
-      <c r="K7" s="8" t="inlineStr"/>
-      <c r="L7" s="8" t="inlineStr"/>
-      <c r="M7" s="8" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
-      <c r="O7" s="8" t="inlineStr"/>
-      <c r="P7" s="8" t="inlineStr"/>
-      <c r="Q7" s="8" t="inlineStr"/>
-      <c r="R7" s="8" t="inlineStr"/>
-      <c r="S7" s="8" t="inlineStr"/>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>H3.0xR8, 청단풍</t>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|청단풍|H2.5XR8</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>청단풍</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>H3.0xR8</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>81407</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>181407</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>1221105</v>
+      </c>
+      <c r="R7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5" t="n">
+        <v>2721105</v>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.08</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>사). 이팝나무</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>H3.0xR8</t>
         </is>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="I8" s="8" t="inlineStr"/>
-      <c r="J8" s="8" t="inlineStr"/>
-      <c r="K8" s="8" t="inlineStr"/>
-      <c r="L8" s="8" t="inlineStr"/>
-      <c r="M8" s="8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
-      <c r="O8" s="8" t="inlineStr"/>
-      <c r="P8" s="8" t="inlineStr"/>
-      <c r="Q8" s="8" t="inlineStr"/>
-      <c r="R8" s="8" t="inlineStr"/>
-      <c r="S8" s="8" t="inlineStr"/>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>H3.0xR8, 이팝나무</t>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|이팝나무|H3.5XR10</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>이팝나무</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>H3.0xR8</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>81407</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>181407</v>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>1709547</v>
+      </c>
+      <c r="R8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5" t="n">
+        <v>3809547</v>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.17</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>아). 복자기</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>H3.5xR8</t>
         </is>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>0.482</v>
-      </c>
-      <c r="I9" s="8" t="inlineStr"/>
-      <c r="J9" s="8" t="inlineStr"/>
-      <c r="K9" s="8" t="inlineStr"/>
-      <c r="L9" s="8" t="inlineStr"/>
-      <c r="M9" s="8" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
-      <c r="O9" s="8" t="inlineStr"/>
-      <c r="P9" s="8" t="inlineStr"/>
-      <c r="Q9" s="8" t="inlineStr"/>
-      <c r="R9" s="8" t="inlineStr"/>
-      <c r="S9" s="8" t="inlineStr"/>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xR8, 복자기</t>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|복자기|H2.5XR8</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>복자기</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xR8</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>81407</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>171407</v>
+      </c>
+      <c r="P9" s="5" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>1628140</v>
+      </c>
+      <c r="R9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5" t="n">
+        <v>3428140</v>
+      </c>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.14</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>자). 영산홍</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>H0.3xW0.3</t>
         </is>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E10" s="3" t="n">
         <v>1770</v>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="I10" s="8" t="inlineStr"/>
-      <c r="J10" s="8" t="inlineStr"/>
-      <c r="K10" s="8" t="inlineStr"/>
-      <c r="L10" s="8" t="inlineStr"/>
-      <c r="M10" s="8" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
-      <c r="O10" s="8" t="inlineStr"/>
-      <c r="P10" s="8" t="inlineStr"/>
-      <c r="Q10" s="8" t="inlineStr"/>
-      <c r="R10" s="8" t="inlineStr"/>
-      <c r="S10" s="8" t="inlineStr"/>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>H0.3xW0.3, 영산홍</t>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|철쭉 영산홍|H0.3XW0.3</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>철쭉 영산홍</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>H0.3xW0.3</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>6676</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>7126</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>796500</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>11816520</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="5" t="n">
+        <v>12613020</v>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.00</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>차). 산철쭉</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>H0.3xW0.3</t>
         </is>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E11" s="3" t="n">
         <v>1250</v>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="I11" s="8" t="inlineStr"/>
-      <c r="J11" s="8" t="inlineStr"/>
-      <c r="K11" s="8" t="inlineStr"/>
-      <c r="L11" s="8" t="inlineStr"/>
-      <c r="M11" s="8" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr"/>
-      <c r="O11" s="8" t="inlineStr"/>
-      <c r="P11" s="8" t="inlineStr"/>
-      <c r="Q11" s="8" t="inlineStr"/>
-      <c r="R11" s="8" t="inlineStr"/>
-      <c r="S11" s="8" t="inlineStr"/>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>H0.3xW0.3, 산철쭉</t>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|철쭉 산철쭉|H0.3XW0.3</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>철쭉 산철쭉</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>H0.3xW0.3</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>6676</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>7076</v>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>8345000</v>
+      </c>
+      <c r="R11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="5" t="n">
+        <v>8845000</v>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.00</t>
         </is>
       </c>
     </row>
@@ -2901,678 +3153,1042 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="n">
+      <c r="A33" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>나). 스트로브잣</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>H3.5xW1.8</t>
         </is>
       </c>
-      <c r="E33" s="8" t="n">
+      <c r="E33" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="n">
-        <v>0.392</v>
-      </c>
-      <c r="I33" s="8" t="inlineStr"/>
-      <c r="J33" s="8" t="inlineStr"/>
-      <c r="K33" s="8" t="inlineStr"/>
-      <c r="L33" s="8" t="inlineStr"/>
-      <c r="M33" s="8" t="inlineStr"/>
-      <c r="N33" s="8" t="inlineStr"/>
-      <c r="O33" s="8" t="inlineStr"/>
-      <c r="P33" s="8" t="inlineStr"/>
-      <c r="Q33" s="8" t="inlineStr"/>
-      <c r="R33" s="8" t="inlineStr"/>
-      <c r="S33" s="8" t="inlineStr"/>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xW1.8, 스트로브잣</t>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|스트로브잣나무|H3.5XW1.8</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>스트로브잣나무</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xW1.8</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>64009</v>
+      </c>
+      <c r="N33" s="5" t="n">
+        <v>6551</v>
+      </c>
+      <c r="O33" s="5" t="n">
+        <v>220560</v>
+      </c>
+      <c r="P33" s="5" t="n">
+        <v>4050000</v>
+      </c>
+      <c r="Q33" s="5" t="n">
+        <v>1728243</v>
+      </c>
+      <c r="R33" s="5" t="n">
+        <v>176877</v>
+      </c>
+      <c r="S33" s="5" t="n">
+        <v>5955120</v>
+      </c>
+      <c r="T33" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.00</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="n">
+      <c r="A34" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>다). 느티나무</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>H4.0xR15</t>
         </is>
       </c>
-      <c r="E34" s="8" t="n">
+      <c r="E34" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G34" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="I34" s="8" t="inlineStr"/>
-      <c r="J34" s="8" t="inlineStr"/>
-      <c r="K34" s="8" t="inlineStr"/>
-      <c r="L34" s="8" t="inlineStr"/>
-      <c r="M34" s="8" t="inlineStr"/>
-      <c r="N34" s="8" t="inlineStr"/>
-      <c r="O34" s="8" t="inlineStr"/>
-      <c r="P34" s="8" t="inlineStr"/>
-      <c r="Q34" s="8" t="inlineStr"/>
-      <c r="R34" s="8" t="inlineStr"/>
-      <c r="S34" s="8" t="inlineStr"/>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>H4.0xR15, 느티나무</t>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|느티나무|R15</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>느티나무</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>H4.0xR15</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>270000</v>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>106589</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>10907</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>387496</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>2970000</v>
+      </c>
+      <c r="Q34" s="5" t="n">
+        <v>1172479</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>119977</v>
+      </c>
+      <c r="S34" s="5" t="n">
+        <v>4262456</v>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.17</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="n">
+      <c r="A35" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>라). 배롱나무</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>H3.0xR10</t>
         </is>
       </c>
-      <c r="E35" s="8" t="n">
+      <c r="E35" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H35" s="8" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="I35" s="8" t="inlineStr"/>
-      <c r="J35" s="8" t="inlineStr"/>
-      <c r="K35" s="8" t="inlineStr"/>
-      <c r="L35" s="8" t="inlineStr"/>
-      <c r="M35" s="8" t="inlineStr"/>
-      <c r="N35" s="8" t="inlineStr"/>
-      <c r="O35" s="8" t="inlineStr"/>
-      <c r="P35" s="8" t="inlineStr"/>
-      <c r="Q35" s="8" t="inlineStr"/>
-      <c r="R35" s="8" t="inlineStr"/>
-      <c r="S35" s="8" t="inlineStr"/>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>H3.0xR10, 배롱나무</t>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|배롱나무|H3.0XR10</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>배롱나무</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>H3.0xR10</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>170000</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>75029</v>
+      </c>
+      <c r="N35" s="5" t="n">
+        <v>7697</v>
+      </c>
+      <c r="O35" s="5" t="n">
+        <v>252726</v>
+      </c>
+      <c r="P35" s="5" t="n">
+        <v>510000</v>
+      </c>
+      <c r="Q35" s="5" t="n">
+        <v>225087</v>
+      </c>
+      <c r="R35" s="5" t="n">
+        <v>23091</v>
+      </c>
+      <c r="S35" s="5" t="n">
+        <v>758178</v>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.00</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="n">
+      <c r="A36" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>마). 왕벚나무</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>H3.5xB8</t>
         </is>
       </c>
-      <c r="E36" s="8" t="n">
+      <c r="E36" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="I36" s="8" t="inlineStr"/>
-      <c r="J36" s="8" t="inlineStr"/>
-      <c r="K36" s="8" t="inlineStr"/>
-      <c r="L36" s="8" t="inlineStr"/>
-      <c r="M36" s="8" t="inlineStr"/>
-      <c r="N36" s="8" t="inlineStr"/>
-      <c r="O36" s="8" t="inlineStr"/>
-      <c r="P36" s="8" t="inlineStr"/>
-      <c r="Q36" s="8" t="inlineStr"/>
-      <c r="R36" s="8" t="inlineStr"/>
-      <c r="S36" s="8" t="inlineStr"/>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xB8, 왕벚나무</t>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|왕벚나무|B8</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>왕벚나무</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xB8</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>130000</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>64009</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>6551</v>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>200560</v>
+      </c>
+      <c r="P36" s="5" t="n">
+        <v>1820000</v>
+      </c>
+      <c r="Q36" s="5" t="n">
+        <v>896126</v>
+      </c>
+      <c r="R36" s="5" t="n">
+        <v>91714</v>
+      </c>
+      <c r="S36" s="5" t="n">
+        <v>2807840</v>
+      </c>
+      <c r="T36" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.17</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="n">
+      <c r="A37" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>바). 청단풍</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>H3.0xR8</t>
         </is>
       </c>
-      <c r="E37" s="8" t="n">
+      <c r="E37" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H37" s="8" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="I37" s="8" t="inlineStr"/>
-      <c r="J37" s="8" t="inlineStr"/>
-      <c r="K37" s="8" t="inlineStr"/>
-      <c r="L37" s="8" t="inlineStr"/>
-      <c r="M37" s="8" t="inlineStr"/>
-      <c r="N37" s="8" t="inlineStr"/>
-      <c r="O37" s="8" t="inlineStr"/>
-      <c r="P37" s="8" t="inlineStr"/>
-      <c r="Q37" s="8" t="inlineStr"/>
-      <c r="R37" s="8" t="inlineStr"/>
-      <c r="S37" s="8" t="inlineStr"/>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>H3.0xR8, 청단풍</t>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|청단풍|H2.5XR8</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>청단풍</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>H3.0xR8</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>81407</v>
+      </c>
+      <c r="N37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="5" t="n">
+        <v>181407</v>
+      </c>
+      <c r="P37" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="Q37" s="5" t="n">
+        <v>407035</v>
+      </c>
+      <c r="R37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="5" t="n">
+        <v>907035</v>
+      </c>
+      <c r="T37" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.08</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="n">
+      <c r="A38" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>사). 이팝나무</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>H3.0xR8</t>
         </is>
       </c>
-      <c r="E38" s="8" t="n">
+      <c r="E38" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="I38" s="8" t="inlineStr"/>
-      <c r="J38" s="8" t="inlineStr"/>
-      <c r="K38" s="8" t="inlineStr"/>
-      <c r="L38" s="8" t="inlineStr"/>
-      <c r="M38" s="8" t="inlineStr"/>
-      <c r="N38" s="8" t="inlineStr"/>
-      <c r="O38" s="8" t="inlineStr"/>
-      <c r="P38" s="8" t="inlineStr"/>
-      <c r="Q38" s="8" t="inlineStr"/>
-      <c r="R38" s="8" t="inlineStr"/>
-      <c r="S38" s="8" t="inlineStr"/>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>H3.0xR8, 이팝나무</t>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|이팝나무|H3.5XR10</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>이팝나무</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>H3.0xR8</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>81407</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="5" t="n">
+        <v>181407</v>
+      </c>
+      <c r="P38" s="5" t="n">
+        <v>600000</v>
+      </c>
+      <c r="Q38" s="5" t="n">
+        <v>488442</v>
+      </c>
+      <c r="R38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="5" t="n">
+        <v>1088442</v>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.17</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="n">
+      <c r="A39" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>아). 꽃사과</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>H3.5xR8</t>
         </is>
       </c>
-      <c r="E39" s="8" t="n">
+      <c r="E39" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="F39" s="8" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H39" s="8" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="I39" s="8" t="inlineStr"/>
-      <c r="J39" s="8" t="inlineStr"/>
-      <c r="K39" s="8" t="inlineStr"/>
-      <c r="L39" s="8" t="inlineStr"/>
-      <c r="M39" s="8" t="inlineStr"/>
-      <c r="N39" s="8" t="inlineStr"/>
-      <c r="O39" s="8" t="inlineStr"/>
-      <c r="P39" s="8" t="inlineStr"/>
-      <c r="Q39" s="8" t="inlineStr"/>
-      <c r="R39" s="8" t="inlineStr"/>
-      <c r="S39" s="8" t="inlineStr"/>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xR8, 꽃사과</t>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|꽃사과|H3.0XR8</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>꽃사과</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xR8</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>80000</v>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>81407</v>
+      </c>
+      <c r="N39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="5" t="n">
+        <v>161407</v>
+      </c>
+      <c r="P39" s="5" t="n">
+        <v>480000</v>
+      </c>
+      <c r="Q39" s="5" t="n">
+        <v>488442</v>
+      </c>
+      <c r="R39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="5" t="n">
+        <v>968442</v>
+      </c>
+      <c r="T39" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.07</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="n">
+      <c r="A40" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>자). 복자기</t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>H3.5xR8</t>
         </is>
       </c>
-      <c r="E40" s="8" t="n">
+      <c r="E40" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>0.482</v>
-      </c>
-      <c r="I40" s="8" t="inlineStr"/>
-      <c r="J40" s="8" t="inlineStr"/>
-      <c r="K40" s="8" t="inlineStr"/>
-      <c r="L40" s="8" t="inlineStr"/>
-      <c r="M40" s="8" t="inlineStr"/>
-      <c r="N40" s="8" t="inlineStr"/>
-      <c r="O40" s="8" t="inlineStr"/>
-      <c r="P40" s="8" t="inlineStr"/>
-      <c r="Q40" s="8" t="inlineStr"/>
-      <c r="R40" s="8" t="inlineStr"/>
-      <c r="S40" s="8" t="inlineStr"/>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xR8, 복자기</t>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|복자기|H2.5XR8</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>복자기</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xR8</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>81407</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="5" t="n">
+        <v>171407</v>
+      </c>
+      <c r="P40" s="5" t="n">
+        <v>450000</v>
+      </c>
+      <c r="Q40" s="5" t="n">
+        <v>407035</v>
+      </c>
+      <c r="R40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="5" t="n">
+        <v>857035</v>
+      </c>
+      <c r="T40" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.14</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="n">
+      <c r="A41" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>차). 모감주나무</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>H3.5xR8</t>
         </is>
       </c>
-      <c r="E41" s="8" t="n">
+      <c r="E41" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="I41" s="8" t="inlineStr"/>
-      <c r="J41" s="8" t="inlineStr"/>
-      <c r="K41" s="8" t="inlineStr"/>
-      <c r="L41" s="8" t="inlineStr"/>
-      <c r="M41" s="8" t="inlineStr"/>
-      <c r="N41" s="8" t="inlineStr"/>
-      <c r="O41" s="8" t="inlineStr"/>
-      <c r="P41" s="8" t="inlineStr"/>
-      <c r="Q41" s="8" t="inlineStr"/>
-      <c r="R41" s="8" t="inlineStr"/>
-      <c r="S41" s="8" t="inlineStr"/>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xR8, 모감주나무</t>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0.849</v>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|모과나무|H3.0XR8</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>모감주나무</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xR8</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>81407</v>
+      </c>
+      <c r="N41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="5" t="n">
+        <v>201407</v>
+      </c>
+      <c r="P41" s="5" t="n">
+        <v>600000</v>
+      </c>
+      <c r="Q41" s="5" t="n">
+        <v>407035</v>
+      </c>
+      <c r="R41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="5" t="n">
+        <v>1007035</v>
+      </c>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t>수종 0.67 규격거리 0.07</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="n">
+      <c r="A42" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>카). 영산홍</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>H0.3xW0.3</t>
         </is>
       </c>
-      <c r="E42" s="8" t="n">
+      <c r="E42" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="I42" s="8" t="inlineStr"/>
-      <c r="J42" s="8" t="inlineStr"/>
-      <c r="K42" s="8" t="inlineStr"/>
-      <c r="L42" s="8" t="inlineStr"/>
-      <c r="M42" s="8" t="inlineStr"/>
-      <c r="N42" s="8" t="inlineStr"/>
-      <c r="O42" s="8" t="inlineStr"/>
-      <c r="P42" s="8" t="inlineStr"/>
-      <c r="Q42" s="8" t="inlineStr"/>
-      <c r="R42" s="8" t="inlineStr"/>
-      <c r="S42" s="8" t="inlineStr"/>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>H0.3xW0.3, 영산홍</t>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|철쭉 영산홍|H0.3XW0.3</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>철쭉 영산홍</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>H0.3xW0.3</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>6676</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="5" t="n">
+        <v>7126</v>
+      </c>
+      <c r="P42" s="5" t="n">
+        <v>72000</v>
+      </c>
+      <c r="Q42" s="5" t="n">
+        <v>1068160</v>
+      </c>
+      <c r="R42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="5" t="n">
+        <v>1140160</v>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.00</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="n">
+      <c r="A43" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>타). 산철쭉</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>H0.3xW0.3</t>
         </is>
       </c>
-      <c r="E43" s="8" t="n">
+      <c r="E43" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="F43" s="8" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="I43" s="8" t="inlineStr"/>
-      <c r="J43" s="8" t="inlineStr"/>
-      <c r="K43" s="8" t="inlineStr"/>
-      <c r="L43" s="8" t="inlineStr"/>
-      <c r="M43" s="8" t="inlineStr"/>
-      <c r="N43" s="8" t="inlineStr"/>
-      <c r="O43" s="8" t="inlineStr"/>
-      <c r="P43" s="8" t="inlineStr"/>
-      <c r="Q43" s="8" t="inlineStr"/>
-      <c r="R43" s="8" t="inlineStr"/>
-      <c r="S43" s="8" t="inlineStr"/>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>H0.3xW0.3, 산철쭉</t>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|철쭉 산철쭉|H0.3XW0.3</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>철쭉 산철쭉</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>H0.3xW0.3</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>6676</v>
+      </c>
+      <c r="N43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="5" t="n">
+        <v>7076</v>
+      </c>
+      <c r="P43" s="5" t="n">
+        <v>320000</v>
+      </c>
+      <c r="Q43" s="5" t="n">
+        <v>5340800</v>
+      </c>
+      <c r="R43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="5" t="n">
+        <v>5660800</v>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.00</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="n">
+      <c r="A44" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>파). 조팝나무</t>
         </is>
       </c>
-      <c r="D44" s="8" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>H0.3xW0.3</t>
         </is>
       </c>
-      <c r="E44" s="8" t="n">
+      <c r="E44" s="3" t="n">
         <v>330</v>
       </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G44" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H44" s="8" t="n">
-        <v>0.512</v>
-      </c>
-      <c r="I44" s="8" t="inlineStr"/>
-      <c r="J44" s="8" t="inlineStr"/>
-      <c r="K44" s="8" t="inlineStr"/>
-      <c r="L44" s="8" t="inlineStr"/>
-      <c r="M44" s="8" t="inlineStr"/>
-      <c r="N44" s="8" t="inlineStr"/>
-      <c r="O44" s="8" t="inlineStr"/>
-      <c r="P44" s="8" t="inlineStr"/>
-      <c r="Q44" s="8" t="inlineStr"/>
-      <c r="R44" s="8" t="inlineStr"/>
-      <c r="S44" s="8" t="inlineStr"/>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>H0.3xW0.3, 조팝나무</t>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|이팝나무|H3.5XR10</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>조팝나무</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>H0.3xW0.3</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>6676</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="5" t="n">
+        <v>106676</v>
+      </c>
+      <c r="P44" s="5" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="Q44" s="5" t="n">
+        <v>2203080</v>
+      </c>
+      <c r="R44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="5" t="n">
+        <v>35203080</v>
+      </c>
+      <c r="T44" s="3" t="inlineStr">
+        <is>
+          <t>수종 0.75 규격거리 0.54</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="n">
+      <c r="A45" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>하). 쥐똥나무</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>H1.2xW0.3</t>
         </is>
       </c>
-      <c r="E45" s="8" t="n">
+      <c r="E45" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F45" s="8" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G45" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H45" s="8" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="I45" s="8" t="inlineStr"/>
-      <c r="J45" s="8" t="inlineStr"/>
-      <c r="K45" s="8" t="inlineStr"/>
-      <c r="L45" s="8" t="inlineStr"/>
-      <c r="M45" s="8" t="inlineStr"/>
-      <c r="N45" s="8" t="inlineStr"/>
-      <c r="O45" s="8" t="inlineStr"/>
-      <c r="P45" s="8" t="inlineStr"/>
-      <c r="Q45" s="8" t="inlineStr"/>
-      <c r="R45" s="8" t="inlineStr"/>
-      <c r="S45" s="8" t="inlineStr"/>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>H1.2xW0.3, 쥐똥나무</t>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|홍가시나무|H1.0XW0.3</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>쥐똥나무</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>H1.2xW0.3</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>61208</v>
+      </c>
+      <c r="N45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="5" t="n">
+        <v>66208</v>
+      </c>
+      <c r="P45" s="5" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="Q45" s="5" t="n">
+        <v>44069760</v>
+      </c>
+      <c r="R45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="5" t="n">
+        <v>47669760</v>
+      </c>
+      <c r="T45" s="3" t="inlineStr">
+        <is>
+          <t>수종 0.44 규격거리 0.08</t>
         </is>
       </c>
     </row>
@@ -4977,210 +5593,322 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="n">
+      <c r="A67" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>다). 스트로브잣</t>
         </is>
       </c>
-      <c r="D67" s="8" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>H3.5xW1.8</t>
         </is>
       </c>
-      <c r="E67" s="8" t="n">
+      <c r="E67" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="F67" s="8" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G67" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H67" s="8" t="n">
-        <v>0.392</v>
-      </c>
-      <c r="I67" s="8" t="inlineStr"/>
-      <c r="J67" s="8" t="inlineStr"/>
-      <c r="K67" s="8" t="inlineStr"/>
-      <c r="L67" s="8" t="inlineStr"/>
-      <c r="M67" s="8" t="inlineStr"/>
-      <c r="N67" s="8" t="inlineStr"/>
-      <c r="O67" s="8" t="inlineStr"/>
-      <c r="P67" s="8" t="inlineStr"/>
-      <c r="Q67" s="8" t="inlineStr"/>
-      <c r="R67" s="8" t="inlineStr"/>
-      <c r="S67" s="8" t="inlineStr"/>
-      <c r="T67" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xW1.8, 스트로브잣</t>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|스트로브잣나무|H3.5XW1.8</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>스트로브잣나무</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xW1.8</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="M67" s="5" t="n">
+        <v>64009</v>
+      </c>
+      <c r="N67" s="5" t="n">
+        <v>6551</v>
+      </c>
+      <c r="O67" s="5" t="n">
+        <v>220560</v>
+      </c>
+      <c r="P67" s="5" t="n">
+        <v>6750000</v>
+      </c>
+      <c r="Q67" s="5" t="n">
+        <v>2880405</v>
+      </c>
+      <c r="R67" s="5" t="n">
+        <v>294795</v>
+      </c>
+      <c r="S67" s="5" t="n">
+        <v>9925200</v>
+      </c>
+      <c r="T67" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.00</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="n">
+      <c r="A68" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C68" s="8" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>라). 복자기</t>
         </is>
       </c>
-      <c r="D68" s="8" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>H3.5xR8</t>
         </is>
       </c>
-      <c r="E68" s="8" t="n">
+      <c r="E68" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="F68" s="8" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G68" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H68" s="8" t="n">
-        <v>0.482</v>
-      </c>
-      <c r="I68" s="8" t="inlineStr"/>
-      <c r="J68" s="8" t="inlineStr"/>
-      <c r="K68" s="8" t="inlineStr"/>
-      <c r="L68" s="8" t="inlineStr"/>
-      <c r="M68" s="8" t="inlineStr"/>
-      <c r="N68" s="8" t="inlineStr"/>
-      <c r="O68" s="8" t="inlineStr"/>
-      <c r="P68" s="8" t="inlineStr"/>
-      <c r="Q68" s="8" t="inlineStr"/>
-      <c r="R68" s="8" t="inlineStr"/>
-      <c r="S68" s="8" t="inlineStr"/>
-      <c r="T68" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xR8, 복자기</t>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|복자기|H2.5XR8</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>복자기</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xR8</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="M68" s="5" t="n">
+        <v>81407</v>
+      </c>
+      <c r="N68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="5" t="n">
+        <v>171407</v>
+      </c>
+      <c r="P68" s="5" t="n">
+        <v>3150000</v>
+      </c>
+      <c r="Q68" s="5" t="n">
+        <v>2849245</v>
+      </c>
+      <c r="R68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" s="5" t="n">
+        <v>5999245</v>
+      </c>
+      <c r="T68" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.14</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="n">
+      <c r="A69" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C69" s="8" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>마). 청단풍</t>
         </is>
       </c>
-      <c r="D69" s="8" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>H3.0xR8</t>
         </is>
       </c>
-      <c r="E69" s="8" t="n">
+      <c r="E69" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="F69" s="8" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G69" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H69" s="8" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="I69" s="8" t="inlineStr"/>
-      <c r="J69" s="8" t="inlineStr"/>
-      <c r="K69" s="8" t="inlineStr"/>
-      <c r="L69" s="8" t="inlineStr"/>
-      <c r="M69" s="8" t="inlineStr"/>
-      <c r="N69" s="8" t="inlineStr"/>
-      <c r="O69" s="8" t="inlineStr"/>
-      <c r="P69" s="8" t="inlineStr"/>
-      <c r="Q69" s="8" t="inlineStr"/>
-      <c r="R69" s="8" t="inlineStr"/>
-      <c r="S69" s="8" t="inlineStr"/>
-      <c r="T69" s="8" t="inlineStr">
-        <is>
-          <t>H3.0xR8, 청단풍</t>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|청단풍|H2.5XR8</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>청단풍</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>H3.0xR8</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M69" s="5" t="n">
+        <v>81407</v>
+      </c>
+      <c r="N69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="5" t="n">
+        <v>181407</v>
+      </c>
+      <c r="P69" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="Q69" s="5" t="n">
+        <v>2849245</v>
+      </c>
+      <c r="R69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" s="5" t="n">
+        <v>6349245</v>
+      </c>
+      <c r="T69" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.08</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="n">
+      <c r="A70" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>바). 산철쭉</t>
         </is>
       </c>
-      <c r="D70" s="8" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>H0.3xW0.3</t>
         </is>
       </c>
-      <c r="E70" s="8" t="n">
+      <c r="E70" s="3" t="n">
         <v>1470</v>
       </c>
-      <c r="F70" s="8" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G70" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H70" s="8" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="I70" s="8" t="inlineStr"/>
-      <c r="J70" s="8" t="inlineStr"/>
-      <c r="K70" s="8" t="inlineStr"/>
-      <c r="L70" s="8" t="inlineStr"/>
-      <c r="M70" s="8" t="inlineStr"/>
-      <c r="N70" s="8" t="inlineStr"/>
-      <c r="O70" s="8" t="inlineStr"/>
-      <c r="P70" s="8" t="inlineStr"/>
-      <c r="Q70" s="8" t="inlineStr"/>
-      <c r="R70" s="8" t="inlineStr"/>
-      <c r="S70" s="8" t="inlineStr"/>
-      <c r="T70" s="8" t="inlineStr">
-        <is>
-          <t>H0.3xW0.3, 산철쭉</t>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|철쭉 산철쭉|H0.3XW0.3</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>철쭉 산철쭉</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>H0.3xW0.3</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="M70" s="5" t="n">
+        <v>6676</v>
+      </c>
+      <c r="N70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="5" t="n">
+        <v>7076</v>
+      </c>
+      <c r="P70" s="5" t="n">
+        <v>588000</v>
+      </c>
+      <c r="Q70" s="5" t="n">
+        <v>9813720</v>
+      </c>
+      <c r="R70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" s="5" t="n">
+        <v>10401720</v>
+      </c>
+      <c r="T70" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.00</t>
         </is>
       </c>
     </row>
@@ -5505,210 +6233,322 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="n">
+      <c r="A75" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>라). 스트로브잣</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>H3.5xW1.8</t>
         </is>
       </c>
-      <c r="E75" s="8" t="n">
+      <c r="E75" s="3" t="n">
         <v>141</v>
       </c>
-      <c r="F75" s="8" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H75" s="8" t="n">
-        <v>0.392</v>
-      </c>
-      <c r="I75" s="8" t="inlineStr"/>
-      <c r="J75" s="8" t="inlineStr"/>
-      <c r="K75" s="8" t="inlineStr"/>
-      <c r="L75" s="8" t="inlineStr"/>
-      <c r="M75" s="8" t="inlineStr"/>
-      <c r="N75" s="8" t="inlineStr"/>
-      <c r="O75" s="8" t="inlineStr"/>
-      <c r="P75" s="8" t="inlineStr"/>
-      <c r="Q75" s="8" t="inlineStr"/>
-      <c r="R75" s="8" t="inlineStr"/>
-      <c r="S75" s="8" t="inlineStr"/>
-      <c r="T75" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xW1.8, 스트로브잣</t>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|스트로브잣나무|H3.5XW1.8</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>스트로브잣나무</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xW1.8</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="M75" s="5" t="n">
+        <v>64009</v>
+      </c>
+      <c r="N75" s="5" t="n">
+        <v>6551</v>
+      </c>
+      <c r="O75" s="5" t="n">
+        <v>220560</v>
+      </c>
+      <c r="P75" s="5" t="n">
+        <v>21150000</v>
+      </c>
+      <c r="Q75" s="5" t="n">
+        <v>9025269</v>
+      </c>
+      <c r="R75" s="5" t="n">
+        <v>923691</v>
+      </c>
+      <c r="S75" s="5" t="n">
+        <v>31098960</v>
+      </c>
+      <c r="T75" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.00</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="8" t="n">
+      <c r="A76" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C76" s="8" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>마). 복자기</t>
         </is>
       </c>
-      <c r="D76" s="8" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>H3.5xR8</t>
         </is>
       </c>
-      <c r="E76" s="8" t="n">
+      <c r="E76" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="F76" s="8" t="inlineStr">
+      <c r="F76" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G76" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H76" s="8" t="n">
-        <v>0.482</v>
-      </c>
-      <c r="I76" s="8" t="inlineStr"/>
-      <c r="J76" s="8" t="inlineStr"/>
-      <c r="K76" s="8" t="inlineStr"/>
-      <c r="L76" s="8" t="inlineStr"/>
-      <c r="M76" s="8" t="inlineStr"/>
-      <c r="N76" s="8" t="inlineStr"/>
-      <c r="O76" s="8" t="inlineStr"/>
-      <c r="P76" s="8" t="inlineStr"/>
-      <c r="Q76" s="8" t="inlineStr"/>
-      <c r="R76" s="8" t="inlineStr"/>
-      <c r="S76" s="8" t="inlineStr"/>
-      <c r="T76" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xR8, 복자기</t>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|복자기|H2.5XR8</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>복자기</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xR8</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="M76" s="5" t="n">
+        <v>81407</v>
+      </c>
+      <c r="N76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="5" t="n">
+        <v>171407</v>
+      </c>
+      <c r="P76" s="5" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="Q76" s="5" t="n">
+        <v>4070350</v>
+      </c>
+      <c r="R76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" s="5" t="n">
+        <v>8570350</v>
+      </c>
+      <c r="T76" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.14</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="8" t="n">
+      <c r="A77" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C77" s="8" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>바). 청단풍</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>H3.0xR8</t>
         </is>
       </c>
-      <c r="E77" s="8" t="n">
+      <c r="E77" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="F77" s="8" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G77" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H77" s="8" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="I77" s="8" t="inlineStr"/>
-      <c r="J77" s="8" t="inlineStr"/>
-      <c r="K77" s="8" t="inlineStr"/>
-      <c r="L77" s="8" t="inlineStr"/>
-      <c r="M77" s="8" t="inlineStr"/>
-      <c r="N77" s="8" t="inlineStr"/>
-      <c r="O77" s="8" t="inlineStr"/>
-      <c r="P77" s="8" t="inlineStr"/>
-      <c r="Q77" s="8" t="inlineStr"/>
-      <c r="R77" s="8" t="inlineStr"/>
-      <c r="S77" s="8" t="inlineStr"/>
-      <c r="T77" s="8" t="inlineStr">
-        <is>
-          <t>H3.0xR8, 청단풍</t>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|청단풍|H2.5XR8</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>청단풍</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>H3.0xR8</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M77" s="5" t="n">
+        <v>81407</v>
+      </c>
+      <c r="N77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="5" t="n">
+        <v>181407</v>
+      </c>
+      <c r="P77" s="5" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="Q77" s="5" t="n">
+        <v>3663315</v>
+      </c>
+      <c r="R77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="5" t="n">
+        <v>8163315</v>
+      </c>
+      <c r="T77" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.08</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="n">
+      <c r="A78" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>사). 산철쭉</t>
         </is>
       </c>
-      <c r="D78" s="8" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>H0.3xW0.3</t>
         </is>
       </c>
-      <c r="E78" s="8" t="n">
+      <c r="E78" s="3" t="n">
         <v>2670</v>
       </c>
-      <c r="F78" s="8" t="inlineStr">
+      <c r="F78" s="3" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G78" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H78" s="8" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="I78" s="8" t="inlineStr"/>
-      <c r="J78" s="8" t="inlineStr"/>
-      <c r="K78" s="8" t="inlineStr"/>
-      <c r="L78" s="8" t="inlineStr"/>
-      <c r="M78" s="8" t="inlineStr"/>
-      <c r="N78" s="8" t="inlineStr"/>
-      <c r="O78" s="8" t="inlineStr"/>
-      <c r="P78" s="8" t="inlineStr"/>
-      <c r="Q78" s="8" t="inlineStr"/>
-      <c r="R78" s="8" t="inlineStr"/>
-      <c r="S78" s="8" t="inlineStr"/>
-      <c r="T78" s="8" t="inlineStr">
-        <is>
-          <t>H0.3xW0.3, 산철쭉</t>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>매칭</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|철쭉 산철쭉|H0.3XW0.3</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>철쭉 산철쭉</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>H0.3xW0.3</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="M78" s="5" t="n">
+        <v>6676</v>
+      </c>
+      <c r="N78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="5" t="n">
+        <v>7076</v>
+      </c>
+      <c r="P78" s="5" t="n">
+        <v>1068000</v>
+      </c>
+      <c r="Q78" s="5" t="n">
+        <v>17824920</v>
+      </c>
+      <c r="R78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="5" t="n">
+        <v>18892920</v>
+      </c>
+      <c r="T78" s="3" t="inlineStr">
+        <is>
+          <t>수종 1.00 규격거리 0.00</t>
         </is>
       </c>
     </row>
@@ -5793,54 +6633,82 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="n">
+      <c r="A80" s="6" t="n">
         <v>105</v>
       </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C80" s="8" t="inlineStr">
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
         <is>
           <t>가). 목백합(튜립)</t>
         </is>
       </c>
-      <c r="D80" s="8" t="inlineStr">
+      <c r="D80" s="6" t="inlineStr">
         <is>
           <t>H5.0xR15</t>
         </is>
       </c>
-      <c r="E80" s="8" t="n">
+      <c r="E80" s="6" t="n">
         <v>144</v>
       </c>
-      <c r="F80" s="8" t="inlineStr">
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <t>주</t>
         </is>
       </c>
-      <c r="G80" s="8" t="inlineStr">
-        <is>
-          <t>미매칭</t>
-        </is>
-      </c>
-      <c r="H80" s="8" t="n">
-        <v>0.501</v>
-      </c>
-      <c r="I80" s="8" t="inlineStr"/>
-      <c r="J80" s="8" t="inlineStr"/>
-      <c r="K80" s="8" t="inlineStr"/>
-      <c r="L80" s="8" t="inlineStr"/>
-      <c r="M80" s="8" t="inlineStr"/>
-      <c r="N80" s="8" t="inlineStr"/>
-      <c r="O80" s="8" t="inlineStr"/>
-      <c r="P80" s="8" t="inlineStr"/>
-      <c r="Q80" s="8" t="inlineStr"/>
-      <c r="R80" s="8" t="inlineStr"/>
-      <c r="S80" s="8" t="inlineStr"/>
-      <c r="T80" s="8" t="inlineStr">
-        <is>
-          <t>H5.0xR15, 튜립, 목백합</t>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>검토</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>FOREST|백목련|H3.5XR15</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>목백합(튜립)</t>
+        </is>
+      </c>
+      <c r="K80" s="6" t="inlineStr">
+        <is>
+          <t>H5.0xR15</t>
+        </is>
+      </c>
+      <c r="L80" s="7" t="n">
+        <v>300000</v>
+      </c>
+      <c r="M80" s="7" t="n">
+        <v>106589</v>
+      </c>
+      <c r="N80" s="7" t="n">
+        <v>10907</v>
+      </c>
+      <c r="O80" s="7" t="n">
+        <v>417496</v>
+      </c>
+      <c r="P80" s="7" t="n">
+        <v>43200000</v>
+      </c>
+      <c r="Q80" s="7" t="n">
+        <v>15348816</v>
+      </c>
+      <c r="R80" s="7" t="n">
+        <v>1570608</v>
+      </c>
+      <c r="S80" s="7" t="n">
+        <v>60119424</v>
+      </c>
+      <c r="T80" s="6" t="inlineStr">
+        <is>
+          <t>수종 0.25 규격거리 0.15</t>
         </is>
       </c>
     </row>
@@ -5908,7 +6776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5918,15 +6786,15 @@
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="4" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="32" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="31" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
@@ -6031,7 +6899,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -6040,73 +6908,73 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>카). 잔디(평떼)</t>
+          <t>나). 스트로브잣</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.3x0.3x0.03</t>
+          <t>H3.5xW1.8</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1100</v>
+        <v>55</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>주</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.955</v>
+        <v>1</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>forestinfo</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>CDK520000000</t>
+          <t>FOREST|스트로브잣나무|H3.5XW1.8</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>잔디붙임</t>
+          <t>스트로브잣나무</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>평떼</t>
+          <t>H3.5xW1.8</t>
         </is>
       </c>
       <c r="L2" s="5" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>5538</v>
+        <v>64009</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>0</v>
+        <v>6551</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>5538</v>
+        <v>220560</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>0</v>
+        <v>8250000</v>
       </c>
       <c r="Q2" s="5" t="n">
-        <v>6091800</v>
+        <v>3520495</v>
       </c>
       <c r="R2" s="5" t="n">
-        <v>0</v>
+        <v>360305</v>
       </c>
       <c r="S2" s="5" t="n">
-        <v>6091800</v>
+        <v>12130800</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -6115,73 +6983,73 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>바). 녹지경계석(직선)</t>
+          <t>다). 느티나무</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>150x150x1000</t>
+          <t>H4.0xR15</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>459</v>
+        <v>7</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>주</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.822</v>
+        <v>0.956</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>forestinfo</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>CLF101103000</t>
+          <t>FOREST|느티나무|R15</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>보차도 및 도로 경계블록</t>
+          <t>느티나무</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>A-Type / 아래폭+높이300㎜ 미만 / 직선구간</t>
+          <t>H4.0xR15</t>
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>659</v>
+        <v>270000</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>6686</v>
+        <v>106589</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>522</v>
+        <v>10907</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>7867</v>
+        <v>387496</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>302481</v>
+        <v>1890000</v>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>3068874</v>
+        <v>746123</v>
       </c>
       <c r="R3" s="5" t="n">
-        <v>239598</v>
+        <v>76349</v>
       </c>
       <c r="S3" s="5" t="n">
-        <v>3610953</v>
+        <v>2712472</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -6190,73 +7058,73 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>사). 포장경계석(직선)</t>
+          <t>라). 배롱나무</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>100x100x1000</t>
+          <t>H3.0xR10</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>주</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.822</v>
+        <v>1</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>forestinfo</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>CLF101103000</t>
+          <t>FOREST|배롱나무|H3.0XR10</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>보차도 및 도로 경계블록</t>
+          <t>배롱나무</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>A-Type / 아래폭+높이300㎜ 미만 / 직선구간</t>
+          <t>H3.0xR10</t>
         </is>
       </c>
       <c r="L4" s="5" t="n">
-        <v>659</v>
+        <v>170000</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>6686</v>
+        <v>75029</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>522</v>
+        <v>7697</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>7867</v>
+        <v>252726</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>6590</v>
+        <v>510000</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>66860</v>
+        <v>225087</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>5220</v>
+        <v>23091</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>78670</v>
+        <v>758178</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -6265,73 +7133,73 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>나). 맹암거(간선)</t>
+          <t>마). 왕벚나무</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>D300</t>
+          <t>H3.5xB8</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>주</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.919</v>
+        <v>0.956</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>forestinfo</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>CGA211003000</t>
+          <t>FOREST|왕벚나무|B8</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>원심력철근콘크리트관/소켓식</t>
+          <t>왕벚나무</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>D300mm / 관부설 및 접합 병행 반복시공</t>
+          <t>H3.5xB8</t>
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>2935</v>
+        <v>130000</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>24310</v>
+        <v>64009</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>3143</v>
+        <v>6551</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>30388</v>
+        <v>200560</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>70440</v>
+        <v>1040000</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>583440</v>
+        <v>512072</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>75432</v>
+        <v>52408</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>729312</v>
+        <v>1604480</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -6340,73 +7208,73 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>다). 맹암거(지선)</t>
+          <t>바). 청단풍</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>D150</t>
+          <t>H3.0xR8</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>주</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.919</v>
+        <v>0.979</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>forestinfo</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>CGC601015000</t>
+          <t>FOREST|청단풍|H2.5XR8</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>파형강관(6m)</t>
+          <t>청단풍</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>D1500/관부설 및 접합 병행 반복시공</t>
+          <t>H3.0xR8</t>
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>3646</v>
+        <v>100000</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>20801</v>
+        <v>81407</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>2221</v>
+        <v>0</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>26668</v>
+        <v>181407</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>116672</v>
+        <v>1500000</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>665632</v>
+        <v>1221105</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>71072</v>
+        <v>0</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>853376</v>
+        <v>2721105</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -6415,73 +7283,73 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>라). 우수관</t>
+          <t>사). 이팝나무</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>D300</t>
+          <t>H3.0xR8</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>주</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.919</v>
+        <v>0.957</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>forestinfo</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>CGA211003000</t>
+          <t>FOREST|이팝나무|H3.5XR10</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>원심력철근콘크리트관/소켓식</t>
+          <t>이팝나무</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>D300mm / 관부설 및 접합 병행 반복시공</t>
+          <t>H3.0xR8</t>
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>2935</v>
+        <v>100000</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>24310</v>
+        <v>81407</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>3143</v>
+        <v>0</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>30388</v>
+        <v>181407</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>179035</v>
+        <v>2100000</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>1482910</v>
+        <v>1709547</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>191723</v>
+        <v>0</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>1853668</v>
+        <v>3809547</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -6490,73 +7358,73 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>마). 산마루측구</t>
+          <t>아). 복자기</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>W300</t>
+          <t>H3.5xR8</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>주</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.771</v>
+        <v>0.964</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>forestinfo</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>CTC30204030S</t>
+          <t>FOREST|복자기|H2.5XR8</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>산마루 측구</t>
+          <t>복자기</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>TYPE-3(H=1.00m)</t>
+          <t>H3.5xR8</t>
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>7581</v>
+        <v>90000</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>207073</v>
+        <v>81407</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>10228</v>
+        <v>0</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>224882</v>
+        <v>171407</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>363888</v>
+        <v>1800000</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>9939504</v>
+        <v>1628140</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>490944</v>
+        <v>0</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>10794336</v>
+        <v>3428140</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -6565,73 +7433,73 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>갸). 잔디(평떼)</t>
+          <t>자). 영산홍</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>0.3x0.3x0.03</t>
+          <t>H0.3xW0.3</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1100</v>
+        <v>1770</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>주</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.955</v>
+        <v>1</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>forestinfo</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>CDK520000000</t>
+          <t>FOREST|철쭉 영산홍|H0.3XW0.3</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>잔디붙임</t>
+          <t>철쭉 영산홍</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>평떼</t>
+          <t>H0.3xW0.3</t>
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>5538</v>
+        <v>6676</v>
       </c>
       <c r="N9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>5538</v>
+        <v>7126</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>0</v>
+        <v>796500</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>6091800</v>
+        <v>11816520</v>
       </c>
       <c r="R9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>6091800</v>
+        <v>12613020</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -6640,73 +7508,73 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>마). 녹지경계석(직선)</t>
+          <t>차). 산철쭉</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>150x150x1000</t>
+          <t>H0.3xW0.3</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>243</v>
+        <v>1250</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>주</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.822</v>
+        <v>1</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>forestinfo</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>CLF101103000</t>
+          <t>FOREST|철쭉 산철쭉|H0.3XW0.3</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>보차도 및 도로 경계블록</t>
+          <t>철쭉 산철쭉</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>A-Type / 아래폭+높이300㎜ 미만 / 직선구간</t>
+          <t>H0.3xW0.3</t>
         </is>
       </c>
       <c r="L10" s="5" t="n">
-        <v>659</v>
+        <v>400</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>6686</v>
+        <v>6676</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>522</v>
+        <v>0</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>7867</v>
+        <v>7076</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>160137</v>
+        <v>500000</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>1624698</v>
+        <v>8345000</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>126846</v>
+        <v>0</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>1911681</v>
+        <v>8845000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -6715,24 +7583,24 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>바). 포장경계석(직선)</t>
+          <t>카). 잔디(평떼)</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>100x100x1000</t>
+          <t>0.3x0.3x0.03</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>29</v>
+        <v>1100</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.822</v>
+        <v>0.955</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
@@ -6741,47 +7609,47 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>CLF101103000</t>
+          <t>CDK520000000</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>보차도 및 도로 경계블록</t>
+          <t>잔디붙임</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>A-Type / 아래폭+높이300㎜ 미만 / 직선구간</t>
+          <t>평떼</t>
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>659</v>
+        <v>0</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>6686</v>
+        <v>5538</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>522</v>
+        <v>0</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>7867</v>
+        <v>5538</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>19111</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>193894</v>
+        <v>6091800</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>15138</v>
+        <v>0</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>228143</v>
+        <v>6091800</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -6790,24 +7658,24 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>나). 맹암거(간선)</t>
+          <t>바). 녹지경계석(직선)</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>D300</t>
+          <t>150x150x1000</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>20</v>
+        <v>459</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>m</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.919</v>
+        <v>0.822</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
@@ -6816,47 +7684,47 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>CGA211003000</t>
+          <t>CLF101103000</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>원심력철근콘크리트관/소켓식</t>
+          <t>보차도 및 도로 경계블록</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>D300mm / 관부설 및 접합 병행 반복시공</t>
+          <t>A-Type / 아래폭+높이300㎜ 미만 / 직선구간</t>
         </is>
       </c>
       <c r="L12" s="5" t="n">
-        <v>2935</v>
+        <v>659</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>24310</v>
+        <v>6686</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>3143</v>
+        <v>522</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>30388</v>
+        <v>7867</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>58700</v>
+        <v>302481</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>486200</v>
+        <v>3068874</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>62860</v>
+        <v>239598</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>607760</v>
+        <v>3610953</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -6865,24 +7733,24 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>다). 맹암거(지선)</t>
+          <t>사). 포장경계석(직선)</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>D150</t>
+          <t>100x100x1000</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>m</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.919</v>
+        <v>0.822</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
@@ -6891,47 +7759,47 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>CGC601015000</t>
+          <t>CLF101103000</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>파형강관(6m)</t>
+          <t>보차도 및 도로 경계블록</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>D1500/관부설 및 접합 병행 반복시공</t>
+          <t>A-Type / 아래폭+높이300㎜ 미만 / 직선구간</t>
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>3646</v>
+        <v>659</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>20801</v>
+        <v>6686</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>2221</v>
+        <v>522</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>26668</v>
+        <v>7867</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>298972</v>
+        <v>6590</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>1705682</v>
+        <v>66860</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>182122</v>
+        <v>5220</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>2186776</v>
+        <v>78670</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -6940,7 +7808,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>라). 우수관</t>
+          <t>나). 맹암거(간선)</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -6949,11 +7817,11 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
@@ -6992,21 +7860,21 @@
         <v>30388</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>258280</v>
+        <v>70440</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>2139280</v>
+        <v>583440</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>276584</v>
+        <v>75432</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>2674144</v>
+        <v>729312</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -7015,24 +7883,24 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>가). 상수리나무(이식)</t>
+          <t>다). 맹암거(지선)</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>R31</t>
+          <t>D150</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>주</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.805</v>
+        <v>0.919</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -7041,47 +7909,47 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>5045D186A0E1EF19C4CD7AFC53E677</t>
+          <t>CGC601015000</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>이식 수간보호</t>
+          <t>파형강관(6m)</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>D1500/관부설 및 접합 병행 반복시공</t>
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>0</v>
+        <v>3646</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>27120</v>
+        <v>20801</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>0</v>
+        <v>2221</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>27120</v>
+        <v>26668</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>0</v>
+        <v>116672</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>1491600</v>
+        <v>665632</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>0</v>
+        <v>71072</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>1491600</v>
+        <v>853376</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -7090,24 +7958,24 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>나). 소나무(이식)</t>
+          <t>라). 우수관</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>R29</t>
+          <t>D300</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>주</t>
+          <t>m</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.805</v>
+        <v>0.919</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
@@ -7116,47 +7984,47 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>5045D186A0E1EF19C4CD7AFC5139E3</t>
+          <t>CGA211003000</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>이식 수간보호</t>
+          <t>원심력철근콘크리트관/소켓식</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>D300mm / 관부설 및 접합 병행 반복시공</t>
         </is>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0</v>
+        <v>2935</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>40355</v>
+        <v>24310</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>0</v>
+        <v>3143</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>40355</v>
+        <v>30388</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>0</v>
+        <v>179035</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>201775</v>
+        <v>1482910</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>0</v>
+        <v>191723</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>201775</v>
+        <v>1853668</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -7165,24 +8033,24 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>사). 법면보호공</t>
+          <t>마). 산마루측구</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>잔디붙임(줄떼)</t>
+          <t>W300</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2900</v>
+        <v>48</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>㎡</t>
+          <t>m</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.89</v>
+        <v>0.771</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -7191,47 +8059,47 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>CDK510000000</t>
+          <t>CTC30204030S</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>잔디붙임</t>
+          <t>산마루 측구</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>줄떼</t>
+          <t>TYPE-3(H=1.00m)</t>
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0</v>
+        <v>7581</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>4699</v>
+        <v>207073</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>0</v>
+        <v>10228</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>4699</v>
+        <v>224882</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>0</v>
+        <v>363888</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>13627100</v>
+        <v>9939504</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>0</v>
+        <v>490944</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>13627100</v>
+        <v>10794336</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -7240,16 +8108,16 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>가). 상수리나무(이식)</t>
+          <t>나). 스트로브잣</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>R27</t>
+          <t>H3.5xW1.8</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>300</v>
+        <v>27</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -7257,56 +8125,56 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.805</v>
+        <v>1</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>forestinfo</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>5045D186A0E1EF19C4CD7AFC5139E3</t>
+          <t>FOREST|스트로브잣나무|H3.5XW1.8</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>이식 수간보호</t>
+          <t>스트로브잣나무</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H3.5xW1.8</t>
         </is>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>40355</v>
+        <v>64009</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>0</v>
+        <v>6551</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>40355</v>
+        <v>220560</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0</v>
+        <v>4050000</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>12106500</v>
+        <v>1728243</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>0</v>
+        <v>176877</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>12106500</v>
+        <v>5955120</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -7315,16 +8183,16 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>나). 상수리나무(이식)</t>
+          <t>다). 느티나무</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>R29</t>
+          <t>H4.0xR15</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -7332,56 +8200,56 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.805</v>
+        <v>0.956</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>forestinfo</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>5045D186A0E1EF19C4CD7AFC5139E3</t>
+          <t>FOREST|느티나무|R15</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>이식 수간보호</t>
+          <t>느티나무</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H4.0xR15</t>
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0</v>
+        <v>270000</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>40355</v>
+        <v>106589</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0</v>
+        <v>10907</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>40355</v>
+        <v>387496</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>0</v>
+        <v>2970000</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>1049230</v>
+        <v>1172479</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>0</v>
+        <v>119977</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>1049230</v>
+        <v>4262456</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -7390,16 +8258,16 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>다). 소나무(이식)</t>
+          <t>라). 배롱나무</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>R25</t>
+          <t>H3.0xR10</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -7407,130 +8275,2380 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.805</v>
+        <v>1</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>forestinfo</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>5045D186A0E1EF19C4CD7AFC5139E3</t>
+          <t>FOREST|배롱나무|H3.0XR10</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>이식 수간보호</t>
+          <t>배롱나무</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H3.0xR10</t>
         </is>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0</v>
+        <v>170000</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>40355</v>
+        <v>75029</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0</v>
+        <v>7697</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>40355</v>
+        <v>252726</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>0</v>
+        <v>510000</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>201775</v>
+        <v>225087</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>0</v>
+        <v>23091</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>201775</v>
+        <v>758178</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>마). 왕벚나무</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xB8</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>forestinfo</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|왕벚나무|B8</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>왕벚나무</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xB8</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>130000</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>64009</v>
+      </c>
+      <c r="N21" s="5" t="n">
+        <v>6551</v>
+      </c>
+      <c r="O21" s="5" t="n">
+        <v>200560</v>
+      </c>
+      <c r="P21" s="5" t="n">
+        <v>1820000</v>
+      </c>
+      <c r="Q21" s="5" t="n">
+        <v>896126</v>
+      </c>
+      <c r="R21" s="5" t="n">
+        <v>91714</v>
+      </c>
+      <c r="S21" s="5" t="n">
+        <v>2807840</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>바). 청단풍</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>H3.0xR8</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>forestinfo</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|청단풍|H2.5XR8</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>청단풍</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>H3.0xR8</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>81407</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="5" t="n">
+        <v>181407</v>
+      </c>
+      <c r="P22" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="Q22" s="5" t="n">
+        <v>407035</v>
+      </c>
+      <c r="R22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="5" t="n">
+        <v>907035</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>사). 이팝나무</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>H3.0xR8</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>forestinfo</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|이팝나무|H3.5XR10</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>이팝나무</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>H3.0xR8</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>81407</v>
+      </c>
+      <c r="N23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="5" t="n">
+        <v>181407</v>
+      </c>
+      <c r="P23" s="5" t="n">
+        <v>600000</v>
+      </c>
+      <c r="Q23" s="5" t="n">
+        <v>488442</v>
+      </c>
+      <c r="R23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="5" t="n">
+        <v>1088442</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>아). 꽃사과</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xR8</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>forestinfo</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|꽃사과|H3.0XR8</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>꽃사과</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xR8</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>80000</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>81407</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>161407</v>
+      </c>
+      <c r="P24" s="5" t="n">
+        <v>480000</v>
+      </c>
+      <c r="Q24" s="5" t="n">
+        <v>488442</v>
+      </c>
+      <c r="R24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="5" t="n">
+        <v>968442</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>자). 복자기</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xR8</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>forestinfo</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|복자기|H2.5XR8</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>복자기</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xR8</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>81407</v>
+      </c>
+      <c r="N25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="5" t="n">
+        <v>171407</v>
+      </c>
+      <c r="P25" s="5" t="n">
+        <v>450000</v>
+      </c>
+      <c r="Q25" s="5" t="n">
+        <v>407035</v>
+      </c>
+      <c r="R25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="5" t="n">
+        <v>857035</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>차). 모감주나무</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xR8</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0.849</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>forestinfo</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|모과나무|H3.0XR8</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>모감주나무</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xR8</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>81407</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="5" t="n">
+        <v>201407</v>
+      </c>
+      <c r="P26" s="5" t="n">
+        <v>600000</v>
+      </c>
+      <c r="Q26" s="5" t="n">
+        <v>407035</v>
+      </c>
+      <c r="R26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="5" t="n">
+        <v>1007035</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>카). 영산홍</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>H0.3xW0.3</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>forestinfo</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|철쭉 영산홍|H0.3XW0.3</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>철쭉 영산홍</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>H0.3xW0.3</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>6676</v>
+      </c>
+      <c r="N27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="5" t="n">
+        <v>7126</v>
+      </c>
+      <c r="P27" s="5" t="n">
+        <v>72000</v>
+      </c>
+      <c r="Q27" s="5" t="n">
+        <v>1068160</v>
+      </c>
+      <c r="R27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="5" t="n">
+        <v>1140160</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>타). 산철쭉</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>H0.3xW0.3</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>forestinfo</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|철쭉 산철쭉|H0.3XW0.3</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>철쭉 산철쭉</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>H0.3xW0.3</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="M28" s="5" t="n">
+        <v>6676</v>
+      </c>
+      <c r="N28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="5" t="n">
+        <v>7076</v>
+      </c>
+      <c r="P28" s="5" t="n">
+        <v>320000</v>
+      </c>
+      <c r="Q28" s="5" t="n">
+        <v>5340800</v>
+      </c>
+      <c r="R28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="5" t="n">
+        <v>5660800</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>파). 조팝나무</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>H0.3xW0.3</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>330</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>forestinfo</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|이팝나무|H3.5XR10</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>조팝나무</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>H0.3xW0.3</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>6676</v>
+      </c>
+      <c r="N29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="5" t="n">
+        <v>106676</v>
+      </c>
+      <c r="P29" s="5" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="Q29" s="5" t="n">
+        <v>2203080</v>
+      </c>
+      <c r="R29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="5" t="n">
+        <v>35203080</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>하). 쥐똥나무</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>H1.2xW0.3</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>720</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>forestinfo</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|홍가시나무|H1.0XW0.3</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>쥐똥나무</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>H1.2xW0.3</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>61208</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>66208</v>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="Q30" s="5" t="n">
+        <v>44069760</v>
+      </c>
+      <c r="R30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="5" t="n">
+        <v>47669760</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>갸). 잔디(평떼)</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>0.3x0.3x0.03</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>CDK520000000</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>잔디붙임</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>평떼</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>5538</v>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="5" t="n">
+        <v>5538</v>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="5" t="n">
+        <v>6091800</v>
+      </c>
+      <c r="R31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="5" t="n">
+        <v>6091800</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>마). 녹지경계석(직선)</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>150x150x1000</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>243</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0.822</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>CLF101103000</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>보차도 및 도로 경계블록</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>A-Type / 아래폭+높이300㎜ 미만 / 직선구간</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>659</v>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>6686</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>522</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>7867</v>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>160137</v>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>1624698</v>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>126846</v>
+      </c>
+      <c r="S32" s="5" t="n">
+        <v>1911681</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>바). 포장경계석(직선)</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>100x100x1000</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0.822</v>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>CLF101103000</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>보차도 및 도로 경계블록</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>A-Type / 아래폭+높이300㎜ 미만 / 직선구간</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>659</v>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>6686</v>
+      </c>
+      <c r="N33" s="5" t="n">
+        <v>522</v>
+      </c>
+      <c r="O33" s="5" t="n">
+        <v>7867</v>
+      </c>
+      <c r="P33" s="5" t="n">
+        <v>19111</v>
+      </c>
+      <c r="Q33" s="5" t="n">
+        <v>193894</v>
+      </c>
+      <c r="R33" s="5" t="n">
+        <v>15138</v>
+      </c>
+      <c r="S33" s="5" t="n">
+        <v>228143</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>나). 맹암거(간선)</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>D300</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>CGA211003000</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>원심력철근콘크리트관/소켓식</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>D300mm / 관부설 및 접합 병행 반복시공</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>2935</v>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>24310</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>3143</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>30388</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>58700</v>
+      </c>
+      <c r="Q34" s="5" t="n">
+        <v>486200</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>62860</v>
+      </c>
+      <c r="S34" s="5" t="n">
+        <v>607760</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>다). 맹암거(지선)</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>CGC601015000</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>파형강관(6m)</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>D1500/관부설 및 접합 병행 반복시공</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>3646</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>20801</v>
+      </c>
+      <c r="N35" s="5" t="n">
+        <v>2221</v>
+      </c>
+      <c r="O35" s="5" t="n">
+        <v>26668</v>
+      </c>
+      <c r="P35" s="5" t="n">
+        <v>298972</v>
+      </c>
+      <c r="Q35" s="5" t="n">
+        <v>1705682</v>
+      </c>
+      <c r="R35" s="5" t="n">
+        <v>182122</v>
+      </c>
+      <c r="S35" s="5" t="n">
+        <v>2186776</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>라). 우수관</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>D300</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>CGA211003000</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>원심력철근콘크리트관/소켓식</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>D300mm / 관부설 및 접합 병행 반복시공</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>2935</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>24310</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>3143</v>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>30388</v>
+      </c>
+      <c r="P36" s="5" t="n">
+        <v>258280</v>
+      </c>
+      <c r="Q36" s="5" t="n">
+        <v>2139280</v>
+      </c>
+      <c r="R36" s="5" t="n">
+        <v>276584</v>
+      </c>
+      <c r="S36" s="5" t="n">
+        <v>2674144</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>가). 상수리나무(이식)</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>R31</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>5045D186A0E1EF19C4CD7AFC53E677</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>이식 수간보호</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>27120</v>
+      </c>
+      <c r="N37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="5" t="n">
+        <v>27120</v>
+      </c>
+      <c r="P37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="5" t="n">
+        <v>1491600</v>
+      </c>
+      <c r="R37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="5" t="n">
+        <v>1491600</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>나). 소나무(이식)</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>R29</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>5045D186A0E1EF19C4CD7AFC5139E3</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>이식 수간보호</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>40355</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="5" t="n">
+        <v>40355</v>
+      </c>
+      <c r="P38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="5" t="n">
+        <v>201775</v>
+      </c>
+      <c r="R38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="5" t="n">
+        <v>201775</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>다). 스트로브잣</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xW1.8</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>forestinfo</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|스트로브잣나무|H3.5XW1.8</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>스트로브잣나무</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xW1.8</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>64009</v>
+      </c>
+      <c r="N39" s="5" t="n">
+        <v>6551</v>
+      </c>
+      <c r="O39" s="5" t="n">
+        <v>220560</v>
+      </c>
+      <c r="P39" s="5" t="n">
+        <v>6750000</v>
+      </c>
+      <c r="Q39" s="5" t="n">
+        <v>2880405</v>
+      </c>
+      <c r="R39" s="5" t="n">
+        <v>294795</v>
+      </c>
+      <c r="S39" s="5" t="n">
+        <v>9925200</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>라). 복자기</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xR8</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>forestinfo</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|복자기|H2.5XR8</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>복자기</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xR8</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>81407</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="5" t="n">
+        <v>171407</v>
+      </c>
+      <c r="P40" s="5" t="n">
+        <v>3150000</v>
+      </c>
+      <c r="Q40" s="5" t="n">
+        <v>2849245</v>
+      </c>
+      <c r="R40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="5" t="n">
+        <v>5999245</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>마). 청단풍</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>H3.0xR8</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>forestinfo</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|청단풍|H2.5XR8</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>청단풍</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>H3.0xR8</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>81407</v>
+      </c>
+      <c r="N41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="5" t="n">
+        <v>181407</v>
+      </c>
+      <c r="P41" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="Q41" s="5" t="n">
+        <v>2849245</v>
+      </c>
+      <c r="R41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="5" t="n">
+        <v>6349245</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>바). 산철쭉</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>H0.3xW0.3</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>1470</v>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>forestinfo</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|철쭉 산철쭉|H0.3XW0.3</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>철쭉 산철쭉</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>H0.3xW0.3</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>6676</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="5" t="n">
+        <v>7076</v>
+      </c>
+      <c r="P42" s="5" t="n">
+        <v>588000</v>
+      </c>
+      <c r="Q42" s="5" t="n">
+        <v>9813720</v>
+      </c>
+      <c r="R42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="5" t="n">
+        <v>10401720</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>사). 법면보호공</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>잔디붙임(줄떼)</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>2900</v>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>㎡</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>CDK510000000</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>잔디붙임</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>줄떼</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>4699</v>
+      </c>
+      <c r="N43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="5" t="n">
+        <v>4699</v>
+      </c>
+      <c r="P43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="5" t="n">
+        <v>13627100</v>
+      </c>
+      <c r="R43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="5" t="n">
+        <v>13627100</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>가). 상수리나무(이식)</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>R27</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>5045D186A0E1EF19C4CD7AFC5139E3</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>이식 수간보호</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>40355</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="5" t="n">
+        <v>40355</v>
+      </c>
+      <c r="P44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="5" t="n">
+        <v>12106500</v>
+      </c>
+      <c r="R44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="5" t="n">
+        <v>12106500</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>나). 상수리나무(이식)</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>R29</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>5045D186A0E1EF19C4CD7AFC5139E3</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>이식 수간보호</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>40355</v>
+      </c>
+      <c r="N45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="5" t="n">
+        <v>40355</v>
+      </c>
+      <c r="P45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="5" t="n">
+        <v>1049230</v>
+      </c>
+      <c r="R45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="5" t="n">
+        <v>1049230</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>다). 소나무(이식)</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>R25</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>5045D186A0E1EF19C4CD7AFC5139E3</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>이식 수간보호</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>40355</v>
+      </c>
+      <c r="N46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="5" t="n">
+        <v>40355</v>
+      </c>
+      <c r="P46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="5" t="n">
+        <v>201775</v>
+      </c>
+      <c r="R46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="5" t="n">
+        <v>201775</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>라). 스트로브잣</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xW1.8</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>forestinfo</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|스트로브잣나무|H3.5XW1.8</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>스트로브잣나무</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xW1.8</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>64009</v>
+      </c>
+      <c r="N47" s="5" t="n">
+        <v>6551</v>
+      </c>
+      <c r="O47" s="5" t="n">
+        <v>220560</v>
+      </c>
+      <c r="P47" s="5" t="n">
+        <v>21150000</v>
+      </c>
+      <c r="Q47" s="5" t="n">
+        <v>9025269</v>
+      </c>
+      <c r="R47" s="5" t="n">
+        <v>923691</v>
+      </c>
+      <c r="S47" s="5" t="n">
+        <v>31098960</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>마). 복자기</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xR8</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>forestinfo</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|복자기|H2.5XR8</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>복자기</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>H3.5xR8</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>81407</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="5" t="n">
+        <v>171407</v>
+      </c>
+      <c r="P48" s="5" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="Q48" s="5" t="n">
+        <v>4070350</v>
+      </c>
+      <c r="R48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="5" t="n">
+        <v>8570350</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>바). 청단풍</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>H3.0xR8</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>forestinfo</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|청단풍|H2.5XR8</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>청단풍</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>H3.0xR8</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M49" s="5" t="n">
+        <v>81407</v>
+      </c>
+      <c r="N49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="5" t="n">
+        <v>181407</v>
+      </c>
+      <c r="P49" s="5" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="Q49" s="5" t="n">
+        <v>3663315</v>
+      </c>
+      <c r="R49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="5" t="n">
+        <v>8163315</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>사). 산철쭉</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>H0.3xW0.3</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>2670</v>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>forestinfo</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>FOREST|철쭉 산철쭉|H0.3XW0.3</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>철쭉 산철쭉</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>H0.3xW0.3</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>6676</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="5" t="n">
+        <v>7076</v>
+      </c>
+      <c r="P50" s="5" t="n">
+        <v>1068000</v>
+      </c>
+      <c r="Q50" s="5" t="n">
+        <v>17824920</v>
+      </c>
+      <c r="R50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="5" t="n">
+        <v>18892920</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
         <v>101</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>아). 법면보호공</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>잔디붙임(줄떼)</t>
         </is>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>7300</v>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>㎡</t>
         </is>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="G51" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I51" s="3" t="inlineStr">
         <is>
           <t>CDK510000000</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J51" s="3" t="inlineStr">
         <is>
           <t>잔디붙임</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K51" s="3" t="inlineStr">
         <is>
           <t>줄떼</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="5" t="n">
+      <c r="L51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="5" t="n">
         <v>4699</v>
       </c>
-      <c r="N21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="5" t="n">
+      <c r="N51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="5" t="n">
         <v>4699</v>
       </c>
-      <c r="P21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="5" t="n">
+      <c r="P51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="5" t="n">
         <v>34302700</v>
       </c>
-      <c r="R21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="5" t="n">
+      <c r="R51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="5" t="n">
         <v>34302700</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S21"/>
+  <autoFilter ref="A1:S51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7541,28 +10659,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="4" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8329,8 +11447,83 @@
         <v>1695600</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>10. 조 경 공</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>가). 목백합(튜립)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>H5.0xR15</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>144</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>forestinfo·검토</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>FOREST|백목련|H3.5XR15</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>목백합(튜립)</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>H5.0xR15</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>300000</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>106589</v>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>10907</v>
+      </c>
+      <c r="O11" s="7" t="n">
+        <v>417496</v>
+      </c>
+      <c r="P11" s="7" t="n">
+        <v>43200000</v>
+      </c>
+      <c r="Q11" s="7" t="n">
+        <v>15348816</v>
+      </c>
+      <c r="R11" s="7" t="n">
+        <v>1570608</v>
+      </c>
+      <c r="S11" s="7" t="n">
+        <v>60119424</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S10"/>
+  <autoFilter ref="A1:S11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8341,14 +11534,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
     <col width="4" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
@@ -8398,7 +11591,7 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
@@ -8407,34 +11600,34 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>나). 스트로브잣</t>
+          <t>가). 생활체육시설A</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>H3.5xW1.8</t>
+          <t>1850*840*H1760</t>
         </is>
       </c>
       <c r="E2" s="8" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>주</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="G2" s="8" t="n">
-        <v>0.392</v>
+        <v>0.438</v>
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>H3.5xW1.8, 스트로브잣</t>
+          <t>1850*840*H1760, 생활체육시설A</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
@@ -8443,34 +11636,34 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>다). 느티나무</t>
+          <t>나). 생활체육시설B</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>H4.0xR15</t>
+          <t>2836*600*H1760</t>
         </is>
       </c>
       <c r="E3" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>주</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="G3" s="8" t="n">
-        <v>0.507</v>
+        <v>0.438</v>
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>H4.0xR15, 느티나무</t>
+          <t>2836*600*H1760, 생활체육시설B</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -8479,34 +11672,34 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>라). 배롱나무</t>
+          <t>다). 생활체육시설C</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>H3.0xR10</t>
+          <t>2200*750*H1760</t>
         </is>
       </c>
       <c r="E4" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>주</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="G4" s="8" t="n">
-        <v>0.507</v>
+        <v>0.438</v>
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>H3.0xR10, 배롱나무</t>
+          <t>2200*750*H1760, 생활체육시설C</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -8515,34 +11708,34 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>마). 왕벚나무</t>
+          <t>라). 생활체육시설D</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>H3.5xB8</t>
+          <t>2470*750*H1760</t>
         </is>
       </c>
       <c r="E5" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>주</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="G5" s="8" t="n">
-        <v>0.507</v>
+        <v>0.438</v>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>H3.5xB8, 왕벚나무</t>
+          <t>2470*750*H1760, 생활체육시설D</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -8551,34 +11744,34 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>바). 청단풍</t>
+          <t>마). 파고라A</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>H3.0xR8</t>
+          <t>5000*3200*H2700</t>
         </is>
       </c>
       <c r="E6" s="8" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>주</t>
+          <t>개소</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
-        <v>0.44</v>
+        <v>0.404</v>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>H3.0xR8, 청단풍</t>
+          <t>5000*3200*H2700, 파고라A</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
@@ -8587,34 +11780,34 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>사). 이팝나무</t>
+          <t>바). 등의자</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>H3.0xR8</t>
+          <t>1600*533*H766</t>
         </is>
       </c>
       <c r="E7" s="8" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>주</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="G7" s="8" t="n">
-        <v>0.507</v>
+        <v>0.421</v>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>H3.0xR8, 이팝나무</t>
+          <t>1600*533*H766, 등의자</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -8623,34 +11816,34 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>아). 복자기</t>
+          <t>사). 플랜터형의자</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>H3.5xR8</t>
+          <t>2200*2200*H700</t>
         </is>
       </c>
       <c r="E8" s="8" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>주</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="G8" s="8" t="n">
-        <v>0.482</v>
+        <v>0.514</v>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>H3.5xR8, 복자기</t>
+          <t>2200*2200*H700, 플랜터형의자</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
@@ -8659,34 +11852,34 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>자). 영산홍</t>
+          <t>나). 투수블럭포장 B</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>H0.3xW0.3</t>
+          <t>T80</t>
         </is>
       </c>
       <c r="E9" s="8" t="n">
-        <v>1770</v>
+        <v>143</v>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>주</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="G9" s="8" t="n">
-        <v>0.418</v>
+        <v>0.546</v>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>H0.3xW0.3, 영산홍</t>
+          <t>T80, 투수블럭포장 B</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
@@ -8695,34 +11888,34 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>차). 산철쭉</t>
+          <t>가). 집수정</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>H0.3xW0.3</t>
+          <t>600*600*H900</t>
         </is>
       </c>
       <c r="E10" s="8" t="n">
-        <v>1250</v>
+        <v>4</v>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>주</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="G10" s="8" t="n">
-        <v>0.418</v>
+        <v>0.527</v>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>H0.3xW0.3, 산철쭉</t>
+          <t>600*600*H900, 집수정</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
@@ -8731,12 +11924,12 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>가). 생활체육시설A</t>
+          <t>가). 생활체육시설E</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>1850*840*H1760</t>
+          <t>1860*1730*H1760</t>
         </is>
       </c>
       <c r="E11" s="8" t="n">
@@ -8748,17 +11941,17 @@
         </is>
       </c>
       <c r="G11" s="8" t="n">
-        <v>0.438</v>
+        <v>0.434</v>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>1850*840*H1760, 생활체육시설A</t>
+          <t>1860*1730*H1760, 생활체육시설E</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -8767,12 +11960,12 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>나). 생활체육시설B</t>
+          <t>나). 생활체육시설F</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>2836*600*H1760</t>
+          <t>2870*860*H1760</t>
         </is>
       </c>
       <c r="E12" s="8" t="n">
@@ -8788,13 +11981,13 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>2836*600*H1760, 생활체육시설B</t>
+          <t>2870*860*H1760, 생활체육시설F</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
@@ -8803,12 +11996,12 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>다). 생활체육시설C</t>
+          <t>다). 생활체육시설G</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>2200*750*H1760</t>
+          <t>1850*560*H1760</t>
         </is>
       </c>
       <c r="E13" s="8" t="n">
@@ -8820,17 +12013,17 @@
         </is>
       </c>
       <c r="G13" s="8" t="n">
-        <v>0.438</v>
+        <v>0.441</v>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>2200*750*H1760, 생활체육시설C</t>
+          <t>1850*560*H1760, 생활체육시설G</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -8839,12 +12032,12 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>라). 생활체육시설D</t>
+          <t>라). 파고라B</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>2470*750*H1760</t>
+          <t>4000*4000*H3200</t>
         </is>
       </c>
       <c r="E14" s="8" t="n">
@@ -8852,21 +12045,21 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>개소</t>
         </is>
       </c>
       <c r="G14" s="8" t="n">
-        <v>0.438</v>
+        <v>0.402</v>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>2470*750*H1760, 생활체육시설D</t>
+          <t>4000*4000*H3200, 파고라B</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
@@ -8875,34 +12068,34 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>마). 파고라A</t>
+          <t>마). 평의자</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>5000*3200*H2700</t>
+          <t>1600*440*H430</t>
         </is>
       </c>
       <c r="E15" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>개소</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="G15" s="8" t="n">
-        <v>0.404</v>
+        <v>0.421</v>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>5000*3200*H2700, 파고라A</t>
+          <t>1600*440*H430, 평의자</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -8920,7 +12113,7 @@
         </is>
       </c>
       <c r="E16" s="8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
@@ -8938,7 +12131,7 @@
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
@@ -8974,7 +12167,7 @@
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
@@ -8983,34 +12176,34 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>나). 투수블럭포장 B</t>
+          <t>아). 안전휀스</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>T80</t>
+          <t>2200*2200*H700</t>
         </is>
       </c>
       <c r="E18" s="8" t="n">
-        <v>143</v>
+        <v>23</v>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>경간</t>
         </is>
       </c>
       <c r="G18" s="8" t="n">
-        <v>0.546</v>
+        <v>0.495</v>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>T80, 투수블럭포장 B</t>
+          <t>2200*2200*H700, 안전휀스</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
@@ -9019,34 +12212,34 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>가). 집수정</t>
+          <t>나). 투수블럭포장 B</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>600*600*H900</t>
+          <t>T80</t>
         </is>
       </c>
       <c r="E19" s="8" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="G19" s="8" t="n">
-        <v>0.527</v>
+        <v>0.546</v>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>600*600*H900, 집수정</t>
+          <t>T80, 투수블럭포장 B</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
@@ -9055,34 +12248,34 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>나). 스트로브잣</t>
+          <t>가). 집수정</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>H3.5xW1.8</t>
+          <t>600*600*H900</t>
         </is>
       </c>
       <c r="E20" s="8" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>주</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="G20" s="8" t="n">
-        <v>0.392</v>
+        <v>0.527</v>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>H3.5xW1.8, 스트로브잣</t>
+          <t>600*600*H900, 집수정</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
-        <v>47</v>
+        <v>107</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
@@ -9091,1149 +12284,33 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>다). 느티나무</t>
+          <t>가). 수목보호판</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>H4.0xR15</t>
+          <t>800*800</t>
         </is>
       </c>
       <c r="E21" s="8" t="n">
-        <v>11</v>
+        <v>144</v>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>주</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="G21" s="8" t="n">
-        <v>0.507</v>
+        <v>0.499</v>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>H4.0xR15, 느티나무</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>라). 배롱나무</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>H3.0xR10</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>주</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>H3.0xR10, 배롱나무</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>마). 왕벚나무</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xB8</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>주</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xB8, 왕벚나무</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>바). 청단풍</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>H3.0xR8</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>주</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>H3.0xR8, 청단풍</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>사). 이팝나무</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>H3.0xR8</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>주</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>H3.0xR8, 이팝나무</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>아). 꽃사과</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xR8</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>주</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xR8, 꽃사과</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="n">
-        <v>53</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>자). 복자기</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xR8</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>주</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="n">
-        <v>0.482</v>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xR8, 복자기</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>차). 모감주나무</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xR8</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>주</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xR8, 모감주나무</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>카). 영산홍</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>H0.3xW0.3</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>160</v>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>주</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>H0.3xW0.3, 영산홍</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>타). 산철쭉</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>H0.3xW0.3</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>800</v>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>주</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>H0.3xW0.3, 산철쭉</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="n">
-        <v>57</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>파). 조팝나무</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>H0.3xW0.3</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>330</v>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>주</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="n">
-        <v>0.512</v>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>H0.3xW0.3, 조팝나무</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>하). 쥐똥나무</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>H1.2xW0.3</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>720</v>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>주</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="H32" s="8" t="inlineStr">
-        <is>
-          <t>H1.2xW0.3, 쥐똥나무</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="n">
-        <v>61</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>가). 생활체육시설E</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>1860*1730*H1760</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="n">
-        <v>0.434</v>
-      </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t>1860*1730*H1760, 생활체육시설E</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="n">
-        <v>62</v>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>나). 생활체육시설F</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>2870*860*H1760</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t>2870*860*H1760, 생활체육시설F</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="n">
-        <v>63</v>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>다). 생활체육시설G</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>1850*560*H1760</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="H35" s="8" t="inlineStr">
-        <is>
-          <t>1850*560*H1760, 생활체육시설G</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="n">
-        <v>64</v>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>라). 파고라B</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>4000*4000*H3200</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>개소</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="H36" s="8" t="inlineStr">
-        <is>
-          <t>4000*4000*H3200, 파고라B</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>마). 평의자</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>1600*440*H430</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>1600*440*H430, 평의자</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="n">
-        <v>66</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>바). 등의자</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>1600*533*H766</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t>1600*533*H766, 등의자</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="8" t="n">
-        <v>67</v>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>사). 플랜터형의자</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>2200*2200*H700</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="n">
-        <v>0.514</v>
-      </c>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t>2200*2200*H700, 플랜터형의자</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="8" t="n">
-        <v>68</v>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>아). 안전휀스</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>2200*2200*H700</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>경간</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t>2200*2200*H700, 안전휀스</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="8" t="n">
-        <v>71</v>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>나). 투수블럭포장 B</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>T80</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="n">
-        <v>0.546</v>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t>T80, 투수블럭포장 B</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="8" t="n">
-        <v>77</v>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>가). 집수정</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>600*600*H900</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="n">
-        <v>0.527</v>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t>600*600*H900, 집수정</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="8" t="n">
-        <v>86</v>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>다). 스트로브잣</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xW1.8</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>주</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="n">
-        <v>0.392</v>
-      </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xW1.8, 스트로브잣</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="n">
-        <v>87</v>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t>라). 복자기</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xR8</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t>주</t>
-        </is>
-      </c>
-      <c r="G44" s="8" t="n">
-        <v>0.482</v>
-      </c>
-      <c r="H44" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xR8, 복자기</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="n">
-        <v>88</v>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>마). 청단풍</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>H3.0xR8</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>주</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H45" s="8" t="inlineStr">
-        <is>
-          <t>H3.0xR8, 청단풍</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="n">
-        <v>89</v>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>바). 산철쭉</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>H0.3xW0.3</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="n">
-        <v>1470</v>
-      </c>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t>주</t>
-        </is>
-      </c>
-      <c r="G46" s="8" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="H46" s="8" t="inlineStr">
-        <is>
-          <t>H0.3xW0.3, 산철쭉</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="n">
-        <v>97</v>
-      </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>라). 스트로브잣</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xW1.8</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="n">
-        <v>141</v>
-      </c>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>주</t>
-        </is>
-      </c>
-      <c r="G47" s="8" t="n">
-        <v>0.392</v>
-      </c>
-      <c r="H47" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xW1.8, 스트로브잣</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="n">
-        <v>98</v>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>마). 복자기</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xR8</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="F48" s="8" t="inlineStr">
-        <is>
-          <t>주</t>
-        </is>
-      </c>
-      <c r="G48" s="8" t="n">
-        <v>0.482</v>
-      </c>
-      <c r="H48" s="8" t="inlineStr">
-        <is>
-          <t>H3.5xR8, 복자기</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="8" t="n">
-        <v>99</v>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>바). 청단풍</t>
-        </is>
-      </c>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>H3.0xR8</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>주</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H49" s="8" t="inlineStr">
-        <is>
-          <t>H3.0xR8, 청단풍</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="inlineStr">
-        <is>
-          <t>사). 산철쭉</t>
-        </is>
-      </c>
-      <c r="D50" s="8" t="inlineStr">
-        <is>
-          <t>H0.3xW0.3</t>
-        </is>
-      </c>
-      <c r="E50" s="8" t="n">
-        <v>2670</v>
-      </c>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>주</t>
-        </is>
-      </c>
-      <c r="G50" s="8" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="H50" s="8" t="inlineStr">
-        <is>
-          <t>H0.3xW0.3, 산철쭉</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="8" t="n">
-        <v>105</v>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="inlineStr">
-        <is>
-          <t>가). 목백합(튜립)</t>
-        </is>
-      </c>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t>H5.0xR15</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="n">
-        <v>144</v>
-      </c>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>주</t>
-        </is>
-      </c>
-      <c r="G51" s="8" t="n">
-        <v>0.501</v>
-      </c>
-      <c r="H51" s="8" t="inlineStr">
-        <is>
-          <t>H5.0xR15, 튜립, 목백합</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="8" t="n">
-        <v>107</v>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>10. 조 경 공</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
-        <is>
-          <t>가). 수목보호판</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t>800*800</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="n">
-        <v>144</v>
-      </c>
-      <c r="F52" s="8" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G52" s="8" t="n">
-        <v>0.499</v>
-      </c>
-      <c r="H52" s="8" t="inlineStr">
-        <is>
           <t>800*800, 수목보호판</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H52"/>
+  <autoFilter ref="A1:H21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>